--- a/Project/Reward_Function.xlsx
+++ b/Project/Reward_Function.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NTU document\Academic stuff (NTU)\Y4S1\Final Year Project\Code\JSSP_Env\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074090BA-FA52-4E9B-A758-ABACB6BCC384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B27D9043-73C9-4CFA-B14D-A1F73C9BCA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="5810" windowWidth="14580" windowHeight="12530" xr2:uid="{0A5D6C9E-0F29-4B1A-A38E-ECAD3E5A169F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0A5D6C9E-0F29-4B1A-A38E-ECAD3E5A169F}"/>
   </bookViews>
   <sheets>
     <sheet name="reward, A2C" sheetId="2" r:id="rId1"/>
